--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -878,7 +878,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://rpps.fr</t>
+    <t>https://rpps.esante.gouv.fr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1012,7 +1012,7 @@
     <t>PractitionerRole.identifier:numeroAm.system</t>
   </si>
   <si>
-    <t>http://ameli.fr</t>
+    <t>https://www.ameli.fr</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:numeroAm.value</t>
@@ -1105,8 +1105,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>dateDebutActivite</t>
@@ -7834,7 +7834,7 @@
         <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>119</v>
@@ -7846,7 +7846,7 @@
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -10983,7 +10983,7 @@
         <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>119</v>
@@ -10995,7 +10995,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -11100,7 +11100,7 @@
         <v>80</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>119</v>
@@ -11330,7 +11330,7 @@
         <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>119</v>
@@ -11560,7 +11560,7 @@
         <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>102</v>
@@ -11677,7 +11677,7 @@
         <v>80</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>119</v>
@@ -11907,7 +11907,7 @@
         <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>119</v>
@@ -12139,7 +12139,7 @@
         <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>102</v>
@@ -12256,7 +12256,7 @@
         <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>119</v>
@@ -12486,7 +12486,7 @@
         <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>119</v>
@@ -12718,7 +12718,7 @@
         <v>90</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>102</v>
@@ -12835,7 +12835,7 @@
         <v>80</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>119</v>
@@ -13065,7 +13065,7 @@
         <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>119</v>
@@ -13297,7 +13297,7 @@
         <v>90</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>102</v>
@@ -13414,7 +13414,7 @@
         <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>119</v>
@@ -13644,7 +13644,7 @@
         <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>119</v>
@@ -13876,7 +13876,7 @@
         <v>90</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>102</v>
@@ -13993,7 +13993,7 @@
         <v>80</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>119</v>
@@ -14223,7 +14223,7 @@
         <v>80</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>119</v>
@@ -14455,7 +14455,7 @@
         <v>90</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>102</v>
@@ -14572,7 +14572,7 @@
         <v>80</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>119</v>
@@ -14802,7 +14802,7 @@
         <v>80</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>119</v>
@@ -15034,7 +15034,7 @@
         <v>90</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>102</v>
@@ -15266,7 +15266,7 @@
         <v>90</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>102</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4893" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4893" uniqueCount="638">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -994,7 +994,7 @@
     <t>[Donnée restreinte] : Identifiant d’activité propre à l’Assurance Maladie. format: 9 digits. synonyme: numeroAM</t>
   </si>
   <si>
-    <t>numeroAM</t>
+    <t>SituationExercice.numeroAM</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:numeroAm.id</t>
@@ -1109,7 +1109,7 @@
 per-1</t>
   </si>
   <si>
-    <t>dateDebutActivite</t>
+    <t>SituationExercice.dateDebutActivite</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -1136,7 +1136,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>dateFinActivite</t>
+    <t>SituationExercice.dateFinActivite</t>
   </si>
   <si>
     <t>DR.2</t>
@@ -1217,6 +1217,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J94-GenreActivite-RASS/FHIR/JDV-J94-GenreActivite-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.genreActivite</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:modeExercice</t>
   </si>
   <si>
@@ -1229,6 +1232,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J95-ModeExercice-RASS/FHIR/JDV-J95-ModeExercice-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.modeExercice</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:typeActiviteLiberale</t>
   </si>
   <si>
@@ -1241,6 +1247,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J96-TypeActiviteLiberale-RASS/FHIR/JDV-J96-TypeActiviteLiberale-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.typeActiviteLiberale</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:statutProfessionnelSSA</t>
   </si>
   <si>
@@ -1253,7 +1262,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J97-StatutProfessionnelSSA-RASS/FHIR/JDV-J97-StatutProfessionnelSSA-RASS</t>
   </si>
   <si>
-    <t>statutPS_SSA</t>
+    <t>SituationExercice.statutPS_SSA</t>
   </si>
   <si>
     <t>PractitionerRole.code:statutHospitalier</t>
@@ -1268,6 +1277,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J98-StatutHospitalier-RASS/FHIR/JDV-J98-StatutHospitalier-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.statutHospitalier</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:fonction</t>
   </si>
   <si>
@@ -1280,7 +1292,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J108-EnsembleFonction-RASS/FHIR/JDV-J108-EnsembleFonction-RASS</t>
   </si>
   <si>
-    <t>role</t>
+    <t>SituationExercice.role</t>
   </si>
   <si>
     <t>PractitionerRole.code:metierPharmacien</t>
@@ -1293,6 +1305,9 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J73-MetierPharmacien-RASS/FHIR/JDV-J73-MetierPharmacien-RASS</t>
+  </si>
+  <si>
+    <t>SituationExercice.metierPharmacien</t>
   </si>
   <si>
     <t>PractitionerRole.specialty</t>
@@ -1384,7 +1399,7 @@
 ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
-    <t>telecommunication</t>
+    <t>SituationExercice.telecommunication</t>
   </si>
   <si>
     <t>XTN</t>
@@ -8540,7 +8555,7 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>380</v>
@@ -8557,13 +8572,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>373</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>78</v>
@@ -8588,7 +8603,7 @@
         <v>261</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M54" t="s" s="2">
         <v>375</v>
@@ -8626,7 +8641,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8659,7 +8674,7 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>380</v>
@@ -8676,13 +8691,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>373</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>78</v>
@@ -8707,7 +8722,7 @@
         <v>261</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>375</v>
@@ -8745,7 +8760,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -8778,7 +8793,7 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>380</v>
@@ -8795,13 +8810,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>373</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>78</v>
@@ -8826,7 +8841,7 @@
         <v>261</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>375</v>
@@ -8864,7 +8879,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8897,7 +8912,7 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>380</v>
@@ -8914,13 +8929,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>373</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>78</v>
@@ -8945,7 +8960,7 @@
         <v>261</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>375</v>
@@ -8983,7 +8998,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -9016,7 +9031,7 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>380</v>
@@ -9033,13 +9048,13 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>373</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>78</v>
@@ -9064,7 +9079,7 @@
         <v>261</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="M58" t="s" s="2">
         <v>375</v>
@@ -9102,7 +9117,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -9135,7 +9150,7 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>380</v>
@@ -9152,13 +9167,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>373</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
@@ -9183,7 +9198,7 @@
         <v>261</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="M59" t="s" s="2">
         <v>375</v>
@@ -9221,7 +9236,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -9254,7 +9269,7 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>380</v>
@@ -9271,10 +9286,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9300,10 +9315,10 @@
         <v>261</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9334,7 +9349,7 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -9352,7 +9367,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9370,13 +9385,13 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9384,10 +9399,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9410,13 +9425,13 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9467,7 +9482,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9488,21 +9503,21 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9525,13 +9540,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9582,7 +9597,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9600,10 +9615,10 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9614,10 +9629,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9640,17 +9655,17 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9687,17 +9702,17 @@
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9709,19 +9724,19 @@
         <v>209</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9729,13 +9744,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>78</v>
@@ -9757,17 +9772,17 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9816,7 +9831,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9828,19 +9843,19 @@
         <v>209</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -9848,10 +9863,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9963,10 +9978,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10080,13 +10095,13 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>78</v>
@@ -10108,13 +10123,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10197,10 +10212,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10312,10 +10327,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10427,10 +10442,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10456,13 +10471,13 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10470,7 +10485,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>78</v>
@@ -10512,7 +10527,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>90</v>
@@ -10544,10 +10559,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10573,10 +10588,10 @@
         <v>154</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10588,7 +10603,7 @@
         <v>78</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>78</v>
@@ -10607,7 +10622,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10625,7 +10640,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10657,13 +10672,13 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>78</v>
@@ -10685,13 +10700,13 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10774,10 +10789,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10889,10 +10904,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11006,13 +11021,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>78</v>
@@ -11037,7 +11052,7 @@
         <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>202</v>
@@ -11123,10 +11138,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11238,10 +11253,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11353,10 +11368,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11382,13 +11397,13 @@
         <v>137</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11396,7 +11411,7 @@
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>78</v>
@@ -11438,7 +11453,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>90</v>
@@ -11470,10 +11485,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11499,10 +11514,10 @@
         <v>261</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11533,7 +11548,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -11551,7 +11566,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11583,13 +11598,13 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>78</v>
@@ -11614,7 +11629,7 @@
         <v>111</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="M80" t="s" s="2">
         <v>202</v>
@@ -11700,10 +11715,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11815,10 +11830,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11930,10 +11945,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11959,13 +11974,13 @@
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11973,7 +11988,7 @@
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>78</v>
@@ -12015,7 +12030,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>90</v>
@@ -12047,10 +12062,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12076,10 +12091,10 @@
         <v>104</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12130,7 +12145,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12162,13 +12177,13 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>78</v>
@@ -12279,10 +12294,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12394,10 +12409,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12509,10 +12524,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12538,13 +12553,13 @@
         <v>137</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12552,7 +12567,7 @@
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>78</v>
@@ -12594,7 +12609,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>90</v>
@@ -12626,10 +12641,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12655,10 +12670,10 @@
         <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12709,7 +12724,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12741,13 +12756,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>78</v>
@@ -12772,7 +12787,7 @@
         <v>111</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="M90" t="s" s="2">
         <v>202</v>
@@ -12858,10 +12873,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12973,10 +12988,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13088,10 +13103,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13117,13 +13132,13 @@
         <v>137</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13131,7 +13146,7 @@
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="S93" t="s" s="2">
         <v>78</v>
@@ -13173,7 +13188,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>90</v>
@@ -13205,10 +13220,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13234,10 +13249,10 @@
         <v>104</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13288,7 +13303,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13320,13 +13335,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>78</v>
@@ -13437,10 +13452,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13552,10 +13567,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13667,10 +13682,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13696,13 +13711,13 @@
         <v>137</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13710,7 +13725,7 @@
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>78</v>
@@ -13752,7 +13767,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>90</v>
@@ -13784,10 +13799,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13813,10 +13828,10 @@
         <v>104</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13867,7 +13882,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13899,13 +13914,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>78</v>
@@ -13930,7 +13945,7 @@
         <v>111</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>202</v>
@@ -14016,10 +14031,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14131,10 +14146,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14246,10 +14261,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14275,13 +14290,13 @@
         <v>137</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14289,7 +14304,7 @@
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>78</v>
@@ -14331,7 +14346,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>90</v>
@@ -14363,10 +14378,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14392,10 +14407,10 @@
         <v>325</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14446,7 +14461,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14478,13 +14493,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>78</v>
@@ -14509,7 +14524,7 @@
         <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>202</v>
@@ -14595,10 +14610,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14710,10 +14725,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14825,10 +14840,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14854,13 +14869,13 @@
         <v>137</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14868,7 +14883,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>78</v>
@@ -14910,7 +14925,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>90</v>
@@ -14942,10 +14957,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14971,10 +14986,10 @@
         <v>325</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15025,7 +15040,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15057,10 +15072,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15086,13 +15101,13 @@
         <v>137</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15100,7 +15115,7 @@
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>78</v>
@@ -15142,7 +15157,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>90</v>
@@ -15174,10 +15189,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15200,13 +15215,13 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15257,7 +15272,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15289,10 +15304,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15318,10 +15333,10 @@
         <v>176</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15333,7 +15348,7 @@
         <v>78</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>78</v>
@@ -15351,10 +15366,10 @@
         <v>254</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>78</v>
@@ -15372,7 +15387,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15381,7 +15396,7 @@
         <v>90</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>102</v>
@@ -15390,13 +15405,13 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>78</v>
@@ -15404,10 +15419,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15433,16 +15448,16 @@
         <v>104</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -15491,7 +15506,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15509,10 +15524,10 @@
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>291</v>
@@ -15523,10 +15538,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15552,16 +15567,16 @@
         <v>176</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15589,10 +15604,10 @@
         <v>254</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15610,7 +15625,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15628,13 +15643,13 @@
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>78</v>
@@ -15642,10 +15657,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15668,16 +15683,16 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15727,7 +15742,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -15759,10 +15774,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15788,10 +15803,10 @@
         <v>294</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15842,7 +15857,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15863,7 +15878,7 @@
         <v>199</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>300</v>
@@ -15874,10 +15889,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15900,16 +15915,16 @@
         <v>78</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15959,7 +15974,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15980,7 +15995,7 @@
         <v>78</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>78</v>
@@ -15991,10 +16006,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16106,10 +16121,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16223,14 +16238,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16252,10 +16267,10 @@
         <v>111</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>114</v>
@@ -16310,7 +16325,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16342,10 +16357,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16371,10 +16386,10 @@
         <v>176</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16404,10 +16419,10 @@
         <v>254</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>78</v>
@@ -16425,7 +16440,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16446,7 +16461,7 @@
         <v>78</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>78</v>
@@ -16457,10 +16472,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16486,10 +16501,10 @@
         <v>325</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16540,7 +16555,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16561,7 +16576,7 @@
         <v>78</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>78</v>
@@ -16572,10 +16587,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16598,16 +16613,16 @@
         <v>78</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -16657,7 +16672,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16678,7 +16693,7 @@
         <v>78</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>78</v>
@@ -16689,10 +16704,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16715,16 +16730,16 @@
         <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -16774,7 +16789,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16795,7 +16810,7 @@
         <v>78</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>78</v>
@@ -16806,10 +16821,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16832,13 +16847,13 @@
         <v>78</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16889,7 +16904,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16910,7 +16925,7 @@
         <v>78</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>78</v>
@@ -16921,10 +16936,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17036,10 +17051,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17153,14 +17168,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17182,10 +17197,10 @@
         <v>111</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>114</v>
@@ -17240,7 +17255,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17272,10 +17287,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17301,10 +17316,10 @@
         <v>104</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17355,7 +17370,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>90</v>
@@ -17387,10 +17402,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17416,10 +17431,10 @@
         <v>294</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17470,7 +17485,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17491,7 +17506,7 @@
         <v>78</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>78</v>
@@ -17502,10 +17517,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17531,10 +17546,10 @@
         <v>104</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17585,7 +17600,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17606,7 +17621,7 @@
         <v>78</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>78</v>
@@ -17617,10 +17632,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17643,17 +17658,17 @@
         <v>78</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -17702,7 +17717,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1195,7 +1195,7 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
